--- a/artfynd/A 28801-2025 artfynd.xlsx
+++ b/artfynd/A 28801-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136887173</v>
       </c>
       <c r="B2" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28801-2025 artfynd.xlsx
+++ b/artfynd/A 28801-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136887173</v>
       </c>
       <c r="B2" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28801-2025 artfynd.xlsx
+++ b/artfynd/A 28801-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136887173</v>
+        <v>137286633</v>
       </c>
       <c r="B2" t="n">
-        <v>58179</v>
+        <v>57213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103023</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +783,116 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137286633</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136887173</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58179</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ragnarök, Råsarna  Holmahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506764</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6310765</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136887173</t>
         </is>
@@ -791,6 +901,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28801-2025 artfynd.xlsx
+++ b/artfynd/A 28801-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137286633</v>
       </c>
       <c r="B2" t="n">
-        <v>57213</v>
+        <v>57223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136887173</v>
       </c>
       <c r="B3" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28801-2025 artfynd.xlsx
+++ b/artfynd/A 28801-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137286633</v>
       </c>
       <c r="B2" t="n">
-        <v>57223</v>
+        <v>57224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136887173</v>
       </c>
       <c r="B3" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28801-2025 artfynd.xlsx
+++ b/artfynd/A 28801-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136887173</v>
       </c>
       <c r="B3" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28801-2025 artfynd.xlsx
+++ b/artfynd/A 28801-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137286633</v>
       </c>
       <c r="B2" t="n">
-        <v>57224</v>
+        <v>57227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
